--- a/Result/checksun_type/ITO導電薄膜.xlsx
+++ b/Result/checksun_type/ITO導電薄膜.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>32.16</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>32.64</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>34.99</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>32.64</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>34.99</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>5050.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4336.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4336.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>5777.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>6847.0</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>6847</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-351.2719648777975</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>5050</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>5050.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>31.72</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>32.68</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>35.1</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>35.1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>5616.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4001.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>4001.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>5931.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7423.62</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>7423.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-411.2842611585756</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>5616</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>5616.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>31.46</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>32.74</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>35.26</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>32.74</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>35.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>2561.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>3993.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>3993</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>5845.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7707.14</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>7707.14</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-542.9702465183082</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>2561</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2561.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>31.64</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>35.47</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>35.47</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>4686.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>4282.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>4282.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>5931.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7956.74</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>7956.74</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-384.3798596565584</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>4686</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>4686.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>31.98</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>33.08</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>35.68</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>35.68</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>3769.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>4989.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>4989.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>5806.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>8223.9</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>8223.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-371.7728834377531</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>3769</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>3769.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>32.35</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>33.24</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>35.88</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>35.88</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3377.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>7218.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>7218.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>6107.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>8475.5</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>8475.5</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-242.23531443097</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3377</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3377.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>32.85</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>33.42</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>36.09</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>5572.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>7861.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>7861.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>6235.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>9406.68</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>9406.68</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-6.530383191601686</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>5572</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>5572.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>33.15</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>33.56</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>36.32</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>36.32</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>4007.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>7697.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>7697.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>6678.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>11379.82</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>11379.82</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>95.24560369291066</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>4007</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>4007.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>33.18</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>33.67</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>36.47</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>36.47</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>8221.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>7579.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>7579.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>6844.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>11648.86</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>11648.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>404.9168133960384</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>8221</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>8221.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>33.13</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>33.78</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>36.62</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>36.62</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>14915.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>6624.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>6624.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>6226.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>12140.42</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>12140.42</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>381.3429410649342</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>14915</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>14915.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>32.96999999999999</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>33.82</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>36.81</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>33.82</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>36.81</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>6591.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>4996.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>4996.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>5294.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>15620.94</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>15620.94</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-383.1676958746775</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>6591</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>6591.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>13.76</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>13.9</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>14.76</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>14.76</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>2035612.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>1742622.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>1742622</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>3623289.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>4611435.6</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>4611435.6</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-730389.703553101</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>2035612</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2035612.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>13.67</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>14.79</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>14.79</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>1130737.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>2006755.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>2006755.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>3720577.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>4673421.5</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>4673421.5</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-747155.6479886342</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>1130737</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>1130737.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>13.62</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>14.01</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>14.83</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>14.83</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>1144970.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>3164286.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>3164286.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>3982209.1</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>4788813.84</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>4788813.84</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-647471.9740398023</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>1144970</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1144970.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>13.61</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>14.07</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>14.87</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>14.87</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>1478293.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>5213697.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>5213697.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>4243254.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>4943161.66</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>4943161.66</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-483467.6907543349</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>1478293</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>1478293.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>13.69</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>14.14</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>14.92</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>14.92</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>2923498.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>5645358.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>5645358.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>4277998.2</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>5044708.62</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>5044708.62</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-267622.3328195838</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>2923498</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>2923498.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>13.77</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>14.97</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>14.97</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>3356279.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>5503956.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>5503956.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>4189681.6</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>5444701.66</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>5444701.66</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-104557.2738835253</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>3356279</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>3356279.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>13.9</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>14.27</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>15.02</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>6918391.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>5434398.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>5434398.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>4271440.4</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>5617822.56</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>5617822.56</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>85757.60580668412</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>6918391</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>6918391.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>14.01</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>15.06</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>11392026.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>4800132.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>4800132</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>4131465.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>5585222.04</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>5585222.04</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-27081.62341468502</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>11392026</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>11392026.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>14.03</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>14.43</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>15.1</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>3636599.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>3272812.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>3272812.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>4238385.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>5473025.66</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>5473025.66</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-666631.3571804017</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>3636599</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>3636599.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,21 +9657,17 @@
           <t>14.01</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>14.48</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
+      <c r="AM22" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="AO22" t="inlineStr">
         <is>
           <t>15.13</t>
         </is>
       </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>15.13</t>
-        </is>
-      </c>
       <c r="AP22" t="inlineStr">
         <is>
           <t>0.55</t>
@@ -9832,20 +9708,16 @@
           <t>2216488.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>2910637.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>2910637.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>4261119.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>5563641.26</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>5563641.26</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-725526.9640892674</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>2216488</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>2216488.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>13.98</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>14.52</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>15.16</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>15.16</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>3008489.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>2875406.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>2875406.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>6471977.8</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>6141477.24</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>6141477.24</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-631597.118098746</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>3008489</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>3008489.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>41.79</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>43.65</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>47.07</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>43.65</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>47.07</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>18788.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>11702.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>11702.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>11910.8</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>21841.68</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>21841.68</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-835.0067717372658</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>18788</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>18788.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>41.26000000000001</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>47.26</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>47.26</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>10470.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>9823.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>9823.799999999999</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>12026.4</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>22264.28</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>22264.28</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-1547.487138612682</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>10470</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>10470.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>41.17</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>43.97</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>47.52</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>47.52</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>5468.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>11849.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>11849.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>12661.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>22603.46</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>22603.46</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-1618.834550627105</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>5468</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>5468.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>41.75</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>44.22</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>44.22</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>47.8</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>12727.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>12695.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>12695.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>17521.5</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>23333.98</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>23333.98</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-1127.015333839599</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>12727</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>12727.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>42.59</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>44.56</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>48.12</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>48.12</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>11061.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>11822.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>11822.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>17187.6</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>24177.16</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>24177.16</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-1161.915905077462</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>11061</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>11061.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>43.29</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>44.84</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>48.39</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>48.39</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>9393.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>12118.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>12118.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>17166.1</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>25730.42</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>25730.42</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-991.7768673787868</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>9393</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>9393.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>44.42</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>45.18</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>48.65</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>48.65</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>20598.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>14229.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>14229</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>17330.2</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>25955.2</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>25955.2</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-534.58621111715</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>20598</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>20598.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>45.3</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>45.46</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>48.9</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>45.46</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>48.9</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>9697.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>13473.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>13473.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>17029.4</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>26019.26</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>26019.26</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-1062.900051774917</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>9697</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>9697.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>45.48</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>45.64</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>49.1</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>8363.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>22347.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>22347.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>17369.8</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>26332.84</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>26332.84</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-611.7091080083301</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>8363</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>8363.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>45.25</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>45.78</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>49.3</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>49.3</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>12543.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>22552.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>22552.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>18149.7</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>27319.1</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>27319.1</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>197.6247083728013</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>12543</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>12543.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>45.05</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>45.85</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>49.54</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>49.54</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>19944.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>22213.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>22213.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>18422.7</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>29048.06</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>29048.06</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>898.9007064753896</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>19944</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>19944.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/ITO導電薄膜.xlsx
+++ b/Result/checksun_type/ITO導電薄膜.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1304.0</t>
+          <t>9186.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>78.67</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>28.26</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1159,35 +1159,35 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>93.72</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>3.31</v>
+        <v>7.54</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.140000000000001</v>
+        <v>10.33</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>37.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>34.32</v>
+        <v>34.72</v>
       </c>
       <c r="BA2" t="n">
-        <v>33.54</v>
+        <v>33.67</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>99.31</t>
+          <t>97.84</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>1.11</v>
+        <v>1.46</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-80.69</t>
+          <t>-74.43</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>33239.97306629834</t>
+          <t>33977.93586206897</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>48560.0</t>
+          <t>378842.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>64463.4</v>
+        <v>128193.4</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>34187.3</t>
+          <t>71747.3</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>11113.94</v>
+        <v>18596</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>30276</t>
+          <t>56446</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>5272.457330792392</t>
+          <t>9593.91669071195</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>9226.878130764682</t>
+          <t>33361.94317026953</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>48560.0</t>
+          <t>378842.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>15.18</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1187.0</t>
+          <t>1304.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>84.82</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>25.73</t>
+          <t>14.20</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>96.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -1650,47 +1650,47 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>2.5</v>
+        <v>3.31</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.93</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>37.46</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>34.08</v>
+        <v>34.32</v>
       </c>
       <c r="BA3" t="n">
-        <v>33.47</v>
+        <v>33.54</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>35.03</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>115.75</t>
+          <t>99.31</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.9</v>
+        <v>1.11</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-85.48</t>
+          <t>-80.69</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>33239.97306629834</t>
+          <t>33977.93586206897</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>44889.0</t>
+          <t>48560.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>55460.4</v>
+        <v>64463.4</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>30007.9</t>
+          <t>34187.3</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>10272.54</v>
+        <v>11113.94</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>25452</t>
+          <t>30276</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>4553.47173079743</t>
+          <t>5272.457330792392</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>9806.039569659017</t>
+          <t>9226.878130764682</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>44889.0</t>
+          <t>48560.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>11.16</t>
+          <t>15.18</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1154.0</t>
+          <t>1187.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>74.36</t>
+          <t>84.82</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,66 +2118,66 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>84.78</t>
+          <t>96.39</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>94.93</t>
+          <t>93.72</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.49</v>
+        <v>6.93</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>33.89</v>
+        <v>34.08</v>
       </c>
       <c r="BA4" t="n">
-        <v>33.42</v>
+        <v>33.47</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>35.03</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>156.63</t>
+          <t>115.75</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-89.68</t>
+          <t>-85.48</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>33239.97306629834</t>
+          <t>33977.93586206897</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>42810.0</t>
+          <t>44889.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>47033.4</v>
+        <v>55460.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>26974.7</t>
+          <t>30007.9</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>9482.120000000001</v>
+        <v>10272.54</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>25452</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>3598.459396458959</t>
+          <t>4553.47173079743</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>10676.51878344882</t>
+          <t>9806.039569659017</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>42810.0</t>
+          <t>44889.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>11.16</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,22 +2297,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3330.0</t>
+          <t>1154.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>70.33</t>
+          <t>74.36</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,87 +2584,87 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>72.17</t>
+          <t>12.56</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.78</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>86.11</t>
+          <t>94.93</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>6.72</v>
+        <v>2.94</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.2</v>
+        <v>5.49</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>35.14</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>33.72</v>
+        <v>33.89</v>
       </c>
       <c r="BA5" t="n">
-        <v>33.37</v>
+        <v>33.42</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>35.09</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>248.01</t>
+          <t>156.63</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-93.72</t>
+          <t>-89.68</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>33239.97306629834</t>
+          <t>33977.93586206897</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>125866.0</t>
+          <t>42810.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>39071</v>
+        <v>47033.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>22938.7</t>
+          <t>26974.7</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>8721.08</v>
+        <v>9482.120000000001</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>16132</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>2311.539507915348</t>
+          <t>3598.459396458959</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>11761.50627516822</t>
+          <t>10676.51878344882</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>125866.0</t>
+          <t>42810.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
+          <t>37.8</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
           <t>38.15</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
-        <is>
-          <t>39.05</t>
-        </is>
-      </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1667.0</t>
+          <t>3330.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>43.37</t>
+          <t>70.33</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3107,51 +3107,51 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>7.23</v>
+        <v>6.72</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.84</v>
+        <v>4.2</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>34.46</t>
+          <t>35.14</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>33.51</v>
+        <v>33.72</v>
       </c>
       <c r="BA6" t="n">
-        <v>33.31</v>
+        <v>33.37</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>451.25</t>
+          <t>248.01</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.38</v>
+        <v>0.63</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-97.61</t>
+          <t>-93.72</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>33239.97306629834</t>
+          <t>33977.93586206897</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>60192.0</t>
+          <t>125866.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>15301.2</v>
+        <v>39071</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>10672.7</t>
+          <t>22938.7</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>6284.02</v>
+        <v>8721.08</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>16132</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>593.3637320511897</t>
+          <t>2311.539507915348</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>3992.577467797077</t>
+          <t>11761.50627516822</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>60192.0</t>
+          <t>125866.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>1667.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-19.15</t>
+          <t>43.37</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-15.58</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,87 +3558,87 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>73.89</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.41</v>
+        <v>7.23</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.25</v>
+        <v>2.84</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>34.46</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>33.32</v>
+        <v>33.51</v>
       </c>
       <c r="BA7" t="n">
-        <v>33.27</v>
+        <v>33.31</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1342.10</t>
+          <t>451.25</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.11</v>
+        <v>0.38</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-100.31</t>
+          <t>-97.61</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>33239.97306629834</t>
+          <t>33977.93586206897</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>60192.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>3911.2</v>
+        <v>15301.2</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>4837.6</t>
+          <t>10672.7</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>5210.4</v>
+        <v>6284.02</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-926</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-24.67512899351711</t>
+          <t>593.3637320511897</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-211.9843094401649</t>
+          <t>3992.577467797077</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>60192.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,22 +3758,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3860,7 +3860,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-19.15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.82</t>
+          <t>-15.58</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>73.89</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0.89</v>
+        <v>-0.41</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>33.60000000000001</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>33.29</v>
+        <v>33.32</v>
       </c>
       <c r="BA8" t="n">
-        <v>33.29</v>
+        <v>33.27</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>35.36</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>371.86</t>
+          <t>1342.10</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-101.33</t>
+          <t>-100.31</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>33239.97306629834</t>
+          <t>33977.93586206897</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>2754.0</t>
+          <t>3545.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>4555.4</v>
+        <v>3911.2</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>4830.4</t>
+          <t>4837.6</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>5228.98</v>
+        <v>5210.4</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-275</t>
+          <t>-926</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>9.381085633146125</t>
+          <t>-24.67512899351711</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-141.6088372990753</t>
+          <t>-211.9843094401649</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>2754.0</t>
+          <t>3545.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-15.20</t>
+          <t>-14.82</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,66 +4553,66 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>80.63</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>0.54</v>
+        <v>0.89</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>33.57000000000001</t>
+          <t>33.60000000000001</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>33.26</v>
+        <v>33.29</v>
       </c>
       <c r="BA9" t="n">
-        <v>33.31</v>
+        <v>33.29</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>35.36</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>188.81</t>
+          <t>371.86</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-102.57</t>
+          <t>-101.33</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>33239.97306629834</t>
+          <t>33977.93586206897</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>2998.0</t>
+          <t>2754.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>6916</v>
+        <v>4555.4</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>4992.4</t>
+          <t>4830.4</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>5392.26</v>
+        <v>5228.98</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>-275</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>36.83379889355002</t>
+          <t>9.381085633146125</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>48.73500994887763</t>
+          <t>-141.6088372990753</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>2998.0</t>
+          <t>2754.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11.89</t>
+          <t>18.08</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.32</t>
+          <t>-15.20</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.67</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>63.77</t>
+          <t>80.63</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>2.1</v>
+        <v>0.54</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>33.57000000000001</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>33.22</v>
+        <v>33.26</v>
       </c>
       <c r="BA10" t="n">
-        <v>33.34</v>
+        <v>33.31</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>128.30</t>
+          <t>188.81</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-103.78</t>
+          <t>-102.57</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>33239.97306629834</t>
+          <t>33977.93586206897</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>7017.0</t>
+          <t>2998.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>6806.4</v>
+        <v>6916</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>5326.7</t>
+          <t>4992.4</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>5441.12</v>
+        <v>5392.26</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>34.66994233803591</t>
+          <t>36.83379889355002</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>292.7713985192077</t>
+          <t>48.73500994887763</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>7017.0</t>
+          <t>2998.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2585.066</t>
+          <t>18233.797</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,177 +5346,177 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>18.6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>84.09</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-03-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-03-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>18.25</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3.29</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>48.96</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>18.25</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>-4.95</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16.1</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>14.95</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2025/04/08</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>16.1</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/09/12</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>15.4</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
         <is>
           <t>2026-01-05 00:00:00</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-03-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-03-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>18.25</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>18.25</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>20.6</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>-4.95</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025/09/05</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>14.95</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2025/04/08</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>13.6</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>2025/09/12</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>84.65</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,12 +5527,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>18234</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5542,51 +5542,51 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>95.65</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>13.64</v>
+        <v>11.11</v>
       </c>
       <c r="AV11" t="n">
-        <v>7.95</v>
+        <v>10.86</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>16.74</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>14.88</v>
+        <v>15.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>14.39</v>
+        <v>14.46</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>103.21</t>
+          <t>100.50</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-70.43</t>
+          <t>-60.50</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,48 +5605,48 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>17868721.82482759</t>
+          <t>18554086.55991736</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>47177441.0</t>
+          <t>343629013.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>21955056.6</v>
+        <v>89597161.8</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>14738988.9</t>
+          <t>48670666.4</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>6368619.18</v>
+        <v>13149547.06</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>7216067</t>
+          <t>40926495</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>1577081.731124248</t>
+          <t>5812181.867202811</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>5578018.082836788</t>
+          <t>29105232.61563491</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>47177441.0</t>
+          <t>343629013.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5706,22 +5706,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3054.351</t>
+          <t>2585.066</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,27 +5843,27 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>48.96</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>100.01</t>
+          <t>14.18</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,12 +6014,12 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>18234</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6029,51 +6029,51 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>92.75</t>
+          <t>95.65</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>7.44</v>
+        <v>13.64</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.32</v>
+        <v>7.95</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>16.06</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>14.67</v>
+        <v>14.88</v>
       </c>
       <c r="BA12" t="n">
-        <v>14.32</v>
+        <v>14.39</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>14.76</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>74.82</t>
+          <t>103.21</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.39</v>
+        <v>0.61</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-78.06</t>
+          <t>-70.43</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,48 +6092,48 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>17868721.82482759</t>
+          <t>18554086.55991736</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>50475012.0</t>
+          <t>47177441.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>13351445.8</v>
+        <v>21955056.6</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>10252627.3</t>
+          <t>14738988.9</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>5539892.56</v>
+        <v>6368619.18</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>3098818</t>
+          <t>7216067</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>849638.7580856045</t>
+          <t>1577081.731124248</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>3531165.104452454</t>
+          <t>5578018.082836788</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>50475012.0</t>
+          <t>47177441.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>197.75</t>
+          <t>3054.351</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>10.75</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-19.35</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>18234</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>86.96</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>92.75</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-0.26</v>
+        <v>7.44</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.13</v>
+        <v>5.32</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>14.54</v>
+        <v>14.67</v>
       </c>
       <c r="BA13" t="n">
-        <v>14.29</v>
+        <v>14.32</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14.76</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>74.82</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-82.16</t>
+          <t>-78.06</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>17868721.82482759</t>
+          <t>18554086.55991736</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>2980200.0</t>
+          <t>50475012.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>4535950.6</v>
+        <v>13351445.8</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>5623974.2</t>
+          <t>10252627.3</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>4700910.96</v>
+        <v>5539892.56</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-1088023</t>
+          <t>3098818</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>362088.5132916319</t>
+          <t>849638.7580856045</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>127665.2030301094</t>
+          <t>3531165.104452454</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>2980200.0</t>
+          <t>50475012.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>245.998</t>
+          <t>197.75</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>-19.35</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>18234</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
+          <t>86.96</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
           <t>91.3</t>
         </is>
       </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>94.2</t>
-        </is>
-      </c>
       <c r="AU14" t="n">
-        <v>-0.13</v>
+        <v>-0.26</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.71</v>
+        <v>4.13</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>14.49</v>
+        <v>14.54</v>
       </c>
       <c r="BA14" t="n">
         <v>14.29</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>14.76</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>67.90</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="BD14" t="n">
         <v>0.27</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-84.35</t>
+          <t>-82.16</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>17868721.82482759</t>
+          <t>18554086.55991736</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>3724143.0</t>
+          <t>2980200.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>6145542.6</v>
+        <v>4535950.6</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>5704942.9</t>
+          <t>5623974.2</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>4687707.3</v>
+        <v>4700910.96</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>440599</t>
+          <t>-1088023</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>404710.9333391815</t>
+          <t>362088.5132916319</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>349692.8723185416</t>
+          <t>127665.2030301094</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>3724143.0</t>
+          <t>2980200.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -7177,12 +7177,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>354.527</t>
+          <t>245.998</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>16.71</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>33.69</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,47 +7475,47 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>18234</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>95.65</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>0.46</v>
+        <v>-0.13</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.87</v>
+        <v>4.71</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>15.17</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>14.43</v>
+        <v>14.49</v>
       </c>
       <c r="BA15" t="n">
         <v>14.29</v>
@@ -7527,14 +7527,14 @@
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>92.09</t>
+          <t>67.90</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-87.01</t>
+          <t>-84.35</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>17868721.82482759</t>
+          <t>18554086.55991736</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>5418487.0</t>
+          <t>3724143.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>7744171</v>
+        <v>6145542.6</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>5792449.0</t>
+          <t>5704942.9</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>4713125.22</v>
+        <v>4687707.3</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>1951722</t>
+          <t>440599</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>414714.217161116</t>
+          <t>404710.9333391815</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>574678.0472906418</t>
+          <t>349692.8723185416</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>5418487.0</t>
+          <t>3724143.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>275.729</t>
+          <t>354.527</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>16.71</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>38.30</t>
+          <t>33.69</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,33 +7941,33 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>18234</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7977,32 +7977,32 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>92.75</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>1.6</v>
+        <v>0.46</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.14</v>
+        <v>4.87</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>14.36</v>
+        <v>14.43</v>
       </c>
       <c r="BA16" t="n">
         <v>14.29</v>
@@ -8014,14 +8014,14 @@
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>124.10</t>
+          <t>92.09</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-90.00</t>
+          <t>-87.01</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>17868721.82482759</t>
+          <t>18554086.55991736</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>4159387.0</t>
+          <t>5418487.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>7522921.2</v>
+        <v>7744171</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>5439467.1</t>
+          <t>5792449.0</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>4638633.98</v>
+        <v>4713125.22</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>2083454</t>
+          <t>1951722</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>385629.884410293</t>
+          <t>414714.217161116</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>694024.3669904033</t>
+          <t>574678.0472906418</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>4159387.0</t>
+          <t>5418487.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,17 +8206,17 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>15.4</t>
+        </is>
+      </c>
+      <c r="CS16" t="inlineStr">
+        <is>
           <t>15.1</t>
-        </is>
-      </c>
-      <c r="CR16" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
-      </c>
-      <c r="CS16" t="inlineStr">
-        <is>
-          <t>14.95</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>423.074</t>
+          <t>275.729</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>36.72</t>
+          <t>38.30</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>18234</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>82.61</t>
+          <t>95.65</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>92.75</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>3.02</v>
+        <v>4.14</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>14.31</v>
+        <v>14.36</v>
       </c>
       <c r="BA17" t="n">
-        <v>14.28</v>
+        <v>14.29</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>14.77</t>
+          <t>14.76</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>173.07</t>
+          <t>124.10</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-93.10</t>
+          <t>-90.00</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>17868721.82482759</t>
+          <t>18554086.55991736</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>6397536.0</t>
+          <t>4159387.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>7153808.8</v>
+        <v>7522921.2</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>5232568.2</t>
+          <t>5439467.1</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>4644213</v>
+        <v>4638633.98</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>1921240</t>
+          <t>2083454</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>329558.1603048184</t>
+          <t>385629.884410293</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>974636.0963118337</t>
+          <t>694024.3669904033</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>6397536.0</t>
+          <t>4159387.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -8628,22 +8628,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,14 +8693,14 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
           <t>15.2</t>
         </is>
       </c>
-      <c r="CR17" t="inlineStr">
-        <is>
-          <t>15.3</t>
-        </is>
-      </c>
       <c r="CS17" t="inlineStr">
         <is>
           <t>14.95</t>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8730,7 +8730,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>732.962</t>
+          <t>423.074</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>35.10</t>
+          <t>36.72</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,68 +8915,68 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>18234</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.61</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>4.52</v>
+        <v>2.1</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.35</v>
+        <v>3.02</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>14.74</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>14.26</v>
+        <v>14.31</v>
       </c>
       <c r="BA18" t="n">
         <v>14.28</v>
@@ -8988,14 +8988,14 @@
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>296.22</t>
+          <t>173.07</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-96.09</t>
+          <t>-93.10</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>17868721.82482759</t>
+          <t>18554086.55991736</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>11028160.0</t>
+          <t>6397536.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>6711997.8</v>
+        <v>7153808.8</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>4968016.1</t>
+          <t>5232568.2</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>4640016.72</v>
+        <v>4644213</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>1743981</t>
+          <t>1921240</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>212271.2628489974</t>
+          <t>329558.1603048184</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>1100899.884759883</t>
+          <t>974636.0963118337</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>11028160.0</t>
+          <t>6397536.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
+      <c r="CS18" t="inlineStr">
+        <is>
+          <t>14.95</t>
+        </is>
+      </c>
+      <c r="CT18" t="inlineStr">
+        <is>
           <t>15.05</t>
-        </is>
-      </c>
-      <c r="CR18" t="inlineStr">
-        <is>
-          <t>15.25</t>
-        </is>
-      </c>
-      <c r="CS18" t="inlineStr">
-        <is>
-          <t>14.65</t>
-        </is>
-      </c>
-      <c r="CT18" t="inlineStr">
-        <is>
-          <t>15.25</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>793.102</t>
+          <t>732.962</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,177 +9242,177 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>15.25</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>18.01</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>35.10</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-03-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-03-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>18.25</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>-4.95</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16.1</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
           <t>14.95</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>18.08</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3.29</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>17.54</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>2025/04/08</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>16.1</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>2025/09/12</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>15.4</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
         <is>
           <t>2026-01-05 00:00:00</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-03-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-03-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>18.25</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>20.6</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>-4.95</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2025/09/05</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>14.95</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>2025/04/08</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>13.6</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>2025/09/12</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,12 +9423,12 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>18234</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -9438,32 +9438,32 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>54.17</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>3.53</v>
+        <v>4.52</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>14.44</t>
+          <t>14.59</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>14.18</v>
+        <v>14.26</v>
       </c>
       <c r="BA19" t="n">
         <v>14.28</v>
@@ -9475,14 +9475,14 @@
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>788.52</t>
+          <t>296.22</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-98.98</t>
+          <t>-96.09</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>17868721.82482759</t>
+          <t>18554086.55991736</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>11717285.0</t>
+          <t>11028160.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>5264343.2</v>
+        <v>6711997.8</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>4478895.4</t>
+          <t>4968016.1</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>4508908.2</v>
+        <v>4640016.72</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>785447</t>
+          <t>1743981</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>50702.42250156361</t>
+          <t>212271.2628489974</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>745820.5866585299</t>
+          <t>1100899.884759883</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>11717285.0</t>
+          <t>11028160.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>56.13</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>14.65</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5578.0</t>
+          <t>2585.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>61.99</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>39.79</t>
+          <t>18.44</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-9.79</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>62.45</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>79.78</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-1.31</v>
+        <v>-2.29</v>
       </c>
       <c r="AV20" t="n">
-        <v>17.76</v>
+        <v>15.98</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>57.96</t>
+          <t>57.72000000000001</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>49.22</v>
+        <v>49.77</v>
       </c>
       <c r="BA20" t="n">
-        <v>46.3</v>
+        <v>46.49</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>47.87</t>
+          <t>47.88</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>64.60</t>
+          <t>45.46</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.07</v>
+        <v>2.34</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-79.69</t>
+          <t>-77.08</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,48 +9988,48 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>321395.3420689655</t>
+          <t>321255.7066115702</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>334338.0</t>
+          <t>146680.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>466300.6</v>
+        <v>393177.8</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>287856.1</t>
+          <t>302007.8</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>70240.32000000001</v>
+        <v>73011.08</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>178444</t>
+          <t>91170</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>46040.59887105948</t>
+          <t>46537.07900027832</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>71729.78600813926</t>
+          <t>49267.71971098188</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>334338.0</t>
+          <t>146680.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -10089,22 +10089,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>408.57</t>
+          <t>402.86</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>51.17</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8030.0</t>
+          <t>5578.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-6.12</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>69.40</t>
+          <t>61.99</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>39.79</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>-9.79</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,266 +10397,266 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>97.86</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>6.49</v>
+        <v>-1.31</v>
       </c>
       <c r="AV21" t="n">
-        <v>17.22</v>
+        <v>17.76</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
+          <t>57.96</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>47.87</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>64.60</t>
+        </is>
+      </c>
+      <c r="BD21" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>-79.69</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2025/12/22</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>321255.7066115702</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>334338.0</t>
+        </is>
+      </c>
+      <c r="BK21" t="n">
+        <v>466300.6</v>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>287856.1</t>
+        </is>
+      </c>
+      <c r="BM21" t="n">
+        <v>70240.32000000001</v>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>178444</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>46040.59887105948</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>71729.78600813926</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>334338.0</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>45.55</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>2025/12/22</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>25.58</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>鑫科</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>鑫科</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BY21" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>-4.817042883161323</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>16.99821580807613</t>
+        </is>
+      </c>
+      <c r="CC21" t="inlineStr">
+        <is>
+          <t>27.20764306852215</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>價跌量縮</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="CG21" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
+          <t>12.31</t>
+        </is>
+      </c>
+      <c r="CI21" t="inlineStr">
+        <is>
+          <t>402.86</t>
+        </is>
+      </c>
+      <c r="CJ21" t="inlineStr">
+        <is>
+          <t>2.61%</t>
+        </is>
+      </c>
+      <c r="CK21" t="inlineStr">
+        <is>
+          <t>-1.64%</t>
+        </is>
+      </c>
+      <c r="CL21" t="inlineStr">
+        <is>
+          <t>50.71</t>
+        </is>
+      </c>
+      <c r="CM21" t="inlineStr">
+        <is>
+          <t>6119</t>
+        </is>
+      </c>
+      <c r="CN21" t="inlineStr">
+        <is>
+          <t>貴金屬材料38.12%、鈦鎳34.48%、金紅石11.48%、薄膜濺鍍靶材10.85%、其他5.08% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO21" t="inlineStr">
+        <is>
+          <t>鑫科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CP21" t="inlineStr">
+        <is>
+          <t>其他電子業平上櫃</t>
+        </is>
+      </c>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="CS21" t="inlineStr">
+        <is>
           <t>57.0</t>
         </is>
       </c>
-      <c r="AZ21" t="n">
-        <v>48.63</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>46.11</v>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>47.85</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>89.53</t>
-        </is>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>-82.97</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>2025/12/22</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>321395.3420689655</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>481054.0</t>
-        </is>
-      </c>
-      <c r="BK21" t="n">
-        <v>432819.8</v>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>255508.3</t>
-        </is>
-      </c>
-      <c r="BM21" t="n">
-        <v>63726.7</v>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>177311</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>41369.83757340861</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>81150.45978950194</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>481054.0</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>45.55</t>
-        </is>
-      </c>
-      <c r="BT21" t="inlineStr">
-        <is>
-          <t>2025/12/22</t>
-        </is>
-      </c>
-      <c r="BU21" t="inlineStr">
-        <is>
-          <t>33.26</t>
-        </is>
-      </c>
-      <c r="BV21" t="inlineStr">
-        <is>
-          <t>鑫科</t>
-        </is>
-      </c>
-      <c r="BW21" t="inlineStr">
-        <is>
-          <t>鑫科</t>
-        </is>
-      </c>
-      <c r="BX21" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BY21" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ21" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="CA21" t="inlineStr">
-        <is>
-          <t>-4.817042883161323</t>
-        </is>
-      </c>
-      <c r="CB21" t="inlineStr">
-        <is>
-          <t>16.99821580807613</t>
-        </is>
-      </c>
-      <c r="CC21" t="inlineStr">
-        <is>
-          <t>27.20764306852215</t>
-        </is>
-      </c>
-      <c r="CD21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
-        </is>
-      </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>3.68</t>
-        </is>
-      </c>
-      <c r="CG21" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="CH21" t="inlineStr">
-        <is>
-          <t>12.31</t>
-        </is>
-      </c>
-      <c r="CI21" t="inlineStr">
-        <is>
-          <t>408.57</t>
-        </is>
-      </c>
-      <c r="CJ21" t="inlineStr">
-        <is>
-          <t>2.61%</t>
-        </is>
-      </c>
-      <c r="CK21" t="inlineStr">
-        <is>
-          <t>-1.64%</t>
-        </is>
-      </c>
-      <c r="CL21" t="inlineStr">
-        <is>
-          <t>51.17</t>
-        </is>
-      </c>
-      <c r="CM21" t="inlineStr">
-        <is>
-          <t>6206</t>
-        </is>
-      </c>
-      <c r="CN21" t="inlineStr">
-        <is>
-          <t>貴金屬材料38.12%、鈦鎳34.48%、金紅石11.48%、薄膜濺鍍靶材10.85%、其他5.08% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO21" t="inlineStr">
-        <is>
-          <t>鑫科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CP21" t="inlineStr">
-        <is>
-          <t>其他電子業平上櫃</t>
-        </is>
-      </c>
-      <c r="CQ21" t="inlineStr">
-        <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="CR21" t="inlineStr">
-        <is>
-          <t>61.9</t>
-        </is>
-      </c>
-      <c r="CS21" t="inlineStr">
-        <is>
-          <t>57.6</t>
-        </is>
-      </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4747.0</t>
+          <t>8030.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,74 +10703,74 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-7.62</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>69.40</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-12-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-07-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>56.8</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5.84</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>80.30</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-07-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-07-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>56.8</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
           <t>67.0</t>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>33.87</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,17 +10884,17 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>94.31</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
@@ -10903,47 +10903,47 @@
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>3.54</v>
+        <v>6.49</v>
       </c>
       <c r="AV22" t="n">
-        <v>14.63</v>
+        <v>17.22</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>54.86</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>47.86</v>
+        <v>48.63</v>
       </c>
       <c r="BA22" t="n">
-        <v>45.85</v>
+        <v>46.11</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>47.77</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>103.04</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>2.74</v>
+        <v>3.29</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-86.78</t>
+          <t>-82.97</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,48 +10962,48 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>321395.3420689655</t>
+          <t>321255.7066115702</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>272632.0</t>
+          <t>481054.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>376958</v>
+        <v>432819.8</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>209075.2</t>
+          <t>255508.3</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>54433.72</v>
+        <v>63726.7</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>167882</t>
+          <t>177311</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>34136.99717048254</t>
+          <t>41369.83757340861</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>75990.76305610931</t>
+          <t>81150.45978950194</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>272632.0</t>
+          <t>481054.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>24.70</t>
+          <t>33.26</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -11063,22 +11063,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>408.57</t>
+          <t>402.86</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>51.17</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12640.0</t>
+          <t>4747.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,22 +11200,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>89.27</t>
+          <t>80.30</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>33.87</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>99.29</t>
+          <t>94.31</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>99.76</t>
+          <t>97.86</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>7.78</v>
+        <v>3.54</v>
       </c>
       <c r="AV23" t="n">
-        <v>12.86</v>
+        <v>14.63</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>53.35</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>47.27</v>
+        <v>47.86</v>
       </c>
       <c r="BA23" t="n">
-        <v>45.66</v>
+        <v>45.85</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>47.73</t>
+          <t>47.77</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>138.46</t>
+          <t>103.04</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>2.39</v>
+        <v>2.74</v>
       </c>
       <c r="BE23" t="n">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-90.18</t>
+          <t>-86.78</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,48 +11449,48 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>321395.3420689655</t>
+          <t>321255.7066115702</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>731185.0</t>
+          <t>272632.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>353736.8</v>
+        <v>376958</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>186898.1</t>
+          <t>209075.2</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>49202.24</v>
+        <v>54433.72</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>166838</t>
+          <t>167882</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>26527.22155491404</t>
+          <t>34136.99717048254</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>88236.7404706873</t>
+          <t>75990.76305610931</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>731185.0</t>
+          <t>272632.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>24.70</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -11555,17 +11555,17 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>408.57</t>
+          <t>402.86</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>51.17</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9087.0</t>
+          <t>12640.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.02</t>
+          <t>89.27</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,87 +11837,87 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>64.83</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.29</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.76</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>13.03</v>
+        <v>7.78</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.050000000000001</v>
+        <v>12.86</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>50.95999999999999</t>
+          <t>53.35</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>46.73</v>
+        <v>47.27</v>
       </c>
       <c r="BA24" t="n">
-        <v>45.46</v>
+        <v>45.66</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>47.69</t>
+          <t>47.73</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>180.11</t>
+          <t>138.46</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>1.83</v>
+        <v>2.39</v>
       </c>
       <c r="BE24" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-93.58</t>
+          <t>-90.18</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>321395.3420689655</t>
+          <t>321255.7066115702</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>512294.0</t>
+          <t>731185.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>210837.8</v>
+        <v>353736.8</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>119783.6</t>
+          <t>186898.1</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>34941.72</v>
+        <v>49202.24</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>91054</t>
+          <t>166838</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>15307.30902477344</t>
+          <t>26527.22155491404</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>53449.00318898856</t>
+          <t>88236.7404706873</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>512294.0</t>
+          <t>731185.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>408.57</t>
+          <t>402.86</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>51.17</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3251.0</t>
+          <t>9087.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>58.32</t>
+          <t>76.02</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>64.83</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12364,47 +12364,47 @@
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>8.74</v>
+        <v>13.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>4.38</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>48.19</t>
+          <t>50.95999999999999</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>46.17</v>
+        <v>46.73</v>
       </c>
       <c r="BA25" t="n">
-        <v>45.26</v>
+        <v>45.46</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>47.69</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>202.90</t>
+          <t>180.11</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>1.09</v>
+        <v>1.83</v>
       </c>
       <c r="BE25" t="n">
-        <v>0.36</v>
+        <v>0.65</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-96.47</t>
+          <t>-93.58</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>321395.3420689655</t>
+          <t>321255.7066115702</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>166934.0</t>
+          <t>512294.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>109411.6</v>
+        <v>210837.8</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>69108.9</t>
+          <t>119783.6</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>25047.98</v>
+        <v>34941.72</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>40302</t>
+          <t>91054</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>8372.455540370695</t>
+          <t>15307.30902477344</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>25295.94981552642</t>
+          <t>53449.00318898856</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>166934.0</t>
+          <t>512294.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>15.04</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -12534,12 +12534,12 @@
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>408.57</t>
+          <t>402.86</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>51.17</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3945.0</t>
+          <t>3251.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>58.32</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12847,51 +12847,51 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>80.41</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>7.71</v>
+        <v>8.74</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.48</v>
+        <v>4.38</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>46.42</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>45.74</v>
+        <v>46.17</v>
       </c>
       <c r="BA26" t="n">
-        <v>45.14</v>
+        <v>45.26</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>269.24</t>
+          <t>202.90</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>0.65</v>
+        <v>1.09</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-98.26</t>
+          <t>-96.47</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>321395.3420689655</t>
+          <t>321255.7066115702</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>201745.0</t>
+          <t>166934.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>78196.8</v>
+        <v>109411.6</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>53380.4</t>
+          <t>69108.9</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>21972.36</v>
+        <v>25047.98</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>24816</t>
+          <t>40302</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>5295.456581251472</t>
+          <t>8372.455540370695</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>21176.73250288313</t>
+          <t>25295.94981552642</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>201745.0</t>
+          <t>166934.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>408.57</t>
+          <t>402.86</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>51.17</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13113,7 +13113,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【b2】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3199.0</t>
+          <t>3945.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>21.83</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,33 +13298,33 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>28.14</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13334,51 +13334,51 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>80.41</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>8.529999999999999</v>
+        <v>7.71</v>
       </c>
       <c r="AV27" t="n">
-        <v>-0.09</v>
+        <v>1.48</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.40</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>45.38</t>
+          <t>46.42</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>45.42</v>
+        <v>45.74</v>
       </c>
       <c r="BA27" t="n">
-        <v>45.08</v>
+        <v>45.14</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>476.30</t>
+          <t>269.24</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>0.33</v>
+        <v>0.65</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-99.43</t>
+          <t>-98.26</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>321395.3420689655</t>
+          <t>321255.7066115702</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>156526.0</t>
+          <t>201745.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>41192.4</v>
+        <v>78196.8</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>33810.1</t>
+          <t>53380.4</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>18366.16</v>
+        <v>21972.36</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>24816</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>2407.951868227535</t>
+          <t>5295.456581251472</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>10806.07446686118</t>
+          <t>21176.73250288313</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>156526.0</t>
+          <t>201745.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>408.57</t>
+          <t>402.86</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>51.17</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>370.0</t>
+          <t>3199.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>21.83</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,66 +13806,66 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>1.7</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="AV28" t="n">
-        <v>-0.59</v>
+        <v>-0.09</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>45.38</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>45.06</v>
+        <v>45.42</v>
       </c>
       <c r="BA28" t="n">
-        <v>45.03</v>
+        <v>45.08</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>66.08</t>
+          <t>476.30</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>-0</v>
+        <v>0.33</v>
       </c>
       <c r="BE28" t="n">
-        <v>-0.01</v>
+        <v>0.06</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-100.11</t>
+          <t>-99.43</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>321395.3420689655</t>
+          <t>321255.7066115702</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>16690.0</t>
+          <t>156526.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>20059.4</v>
+        <v>41192.4</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>19361.0</t>
+          <t>33810.1</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>15600.48</v>
+        <v>18366.16</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>881.0204866577817</t>
+          <t>2407.951868227535</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>449.8103272990775</t>
+          <t>10806.07446686118</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>16690.0</t>
+          <t>156526.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>408.57</t>
+          <t>402.86</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>51.17</t>
+          <t>50.71</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">

--- a/Result/checksun_type/ITO導電薄膜.xlsx
+++ b/Result/checksun_type/ITO導電薄膜.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2007.0</t>
+          <t>4139.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,74 +963,74 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>42.65</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>51.02</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-08-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>39.9</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>3.16</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3.9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>50.61</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-08-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>39.9</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>39.9</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>42.45</t>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,17 +1144,17 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -1163,47 +1163,47 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2.86</v>
+        <v>6.73</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.58</v>
+        <v>12.34</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-3.40</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>38.79000000000001</t>
+          <t>39.96</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>35.08</v>
+        <v>35.57</v>
       </c>
       <c r="BA2" t="n">
-        <v>33.78</v>
+        <v>33.95</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>34.96</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>76.68</t>
+          <t>73.11</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.91</v>
+        <v>1.12</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-68.37</t>
+          <t>-61.30</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,48 +1222,48 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>43310.31006160165</t>
+          <t>43751.04405737705</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>80568.0</t>
+          <t>172259.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>119133.8</v>
+        <v>145023.6</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>79102.4</t>
+          <t>96028.5</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>20065.04</v>
+        <v>23337.16</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>40031</t>
+          <t>48995</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>12279.75875655107</t>
+          <t>14826.77752163201</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>27051.8901186662</t>
+          <t>28835.3807295772</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>80568.0</t>
+          <t>172259.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9186.0</t>
+          <t>2007.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,27 +1460,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>78.67</t>
+          <t>50.61</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,66 +1631,66 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.89</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>7.54</v>
+        <v>2.86</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.33</v>
+        <v>10.58</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>38.79000000000001</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>34.72</v>
+        <v>35.08</v>
       </c>
       <c r="BA3" t="n">
-        <v>33.67</v>
+        <v>33.78</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>34.99</t>
+          <t>34.96</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>97.84</t>
+          <t>76.68</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.74</v>
+        <v>0.91</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-74.43</t>
+          <t>-68.37</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,48 +1709,48 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>43310.31006160165</t>
+          <t>43751.04405737705</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>378842.0</t>
+          <t>80568.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>128193.4</v>
+        <v>119133.8</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>71747.3</t>
+          <t>79102.4</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>18596</v>
+        <v>20065.04</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>56446</t>
+          <t>40031</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>9593.91669071195</t>
+          <t>12279.75875655107</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>33361.94317026953</t>
+          <t>27051.8901186662</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>378842.0</t>
+          <t>80568.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1304.0</t>
+          <t>9186.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>78.67</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>14.20</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,12 +2118,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2133,35 +2133,35 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>93.72</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>3.31</v>
+        <v>7.54</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.140000000000001</v>
+        <v>10.33</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>37.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>34.32</v>
+        <v>34.72</v>
       </c>
       <c r="BA4" t="n">
-        <v>33.54</v>
+        <v>33.67</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>99.31</t>
+          <t>97.84</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>1.11</v>
+        <v>1.46</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-80.69</t>
+          <t>-74.43</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>43310.31006160165</t>
+          <t>43751.04405737705</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>48560.0</t>
+          <t>378842.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>64463.4</v>
+        <v>128193.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>34187.3</t>
+          <t>71747.3</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>11113.94</v>
+        <v>18596</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>30276</t>
+          <t>56446</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>5272.457330792392</t>
+          <t>9593.91669071195</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>9226.878130764682</t>
+          <t>33361.94317026953</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>48560.0</t>
+          <t>378842.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>15.18</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2297,22 +2297,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1187.0</t>
+          <t>1304.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>84.82</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>14.20</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,17 +2605,17 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>96.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
@@ -2624,47 +2624,47 @@
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>2.5</v>
+        <v>3.31</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.93</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>37.46</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>34.08</v>
+        <v>34.32</v>
       </c>
       <c r="BA5" t="n">
-        <v>33.47</v>
+        <v>33.54</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>35.03</t>
+          <t>34.99</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>115.75</t>
+          <t>99.31</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.9</v>
+        <v>1.11</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-85.48</t>
+          <t>-80.69</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>43310.31006160165</t>
+          <t>43751.04405737705</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>44889.0</t>
+          <t>48560.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>55460.4</v>
+        <v>64463.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>30007.9</t>
+          <t>34187.3</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>10272.54</v>
+        <v>11113.94</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>25452</t>
+          <t>30276</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>4553.47173079743</t>
+          <t>5272.457330792392</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>9806.039569659017</t>
+          <t>9226.878130764682</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>44889.0</t>
+          <t>48560.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>11.16</t>
+          <t>15.18</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1154.0</t>
+          <t>1187.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.36</t>
+          <t>84.82</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>12.56</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,66 +3092,66 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>84.78</t>
+          <t>96.39</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>94.93</t>
+          <t>93.72</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.49</v>
+        <v>6.93</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>33.89</v>
+        <v>34.08</v>
       </c>
       <c r="BA6" t="n">
-        <v>33.42</v>
+        <v>33.47</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>35.03</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>156.63</t>
+          <t>115.75</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-89.68</t>
+          <t>-85.48</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>43310.31006160165</t>
+          <t>43751.04405737705</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>42810.0</t>
+          <t>44889.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>47033.4</v>
+        <v>55460.4</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>26974.7</t>
+          <t>30007.9</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>9482.120000000001</v>
+        <v>10272.54</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>25452</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>3598.459396458959</t>
+          <t>4553.47173079743</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>10676.51878344882</t>
+          <t>9806.039569659017</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>42810.0</t>
+          <t>44889.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>11.16</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3330.0</t>
+          <t>1154.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>70.33</t>
+          <t>74.36</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,87 +3558,87 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>12.56</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.78</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>86.11</t>
+          <t>94.93</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>6.72</v>
+        <v>2.94</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.2</v>
+        <v>5.49</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>35.14</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>33.72</v>
+        <v>33.89</v>
       </c>
       <c r="BA7" t="n">
-        <v>33.37</v>
+        <v>33.42</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>35.09</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>248.01</t>
+          <t>156.63</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-93.72</t>
+          <t>-89.68</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>43310.31006160165</t>
+          <t>43751.04405737705</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>125866.0</t>
+          <t>42810.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>39071</v>
+        <v>47033.4</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>22938.7</t>
+          <t>26974.7</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>8721.08</v>
+        <v>9482.120000000001</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>16132</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>2311.539507915348</t>
+          <t>3598.459396458959</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>11761.50627516822</t>
+          <t>10676.51878344882</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>125866.0</t>
+          <t>42810.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
+          <t>37.8</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
           <t>38.15</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
-        <is>
-          <t>39.05</t>
-        </is>
-      </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1667.0</t>
+          <t>3330.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>43.37</t>
+          <t>70.33</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4081,51 +4081,51 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>7.23</v>
+        <v>6.72</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.84</v>
+        <v>4.2</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>34.46</t>
+          <t>35.14</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>33.51</v>
+        <v>33.72</v>
       </c>
       <c r="BA8" t="n">
-        <v>33.31</v>
+        <v>33.37</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>451.25</t>
+          <t>248.01</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.38</v>
+        <v>0.63</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-97.61</t>
+          <t>-93.72</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>43310.31006160165</t>
+          <t>43751.04405737705</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>60192.0</t>
+          <t>125866.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>15301.2</v>
+        <v>39071</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>10672.7</t>
+          <t>22938.7</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>6284.02</v>
+        <v>8721.08</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>16132</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>593.3637320511897</t>
+          <t>2311.539507915348</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>3992.577467797077</t>
+          <t>11761.50627516822</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>60192.0</t>
+          <t>125866.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>11.61</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>1667.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-19.15</t>
+          <t>43.37</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,87 +4532,87 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>73.89</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.41</v>
+        <v>7.23</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.25</v>
+        <v>2.84</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>34.46</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>33.32</v>
+        <v>33.51</v>
       </c>
       <c r="BA9" t="n">
-        <v>33.27</v>
+        <v>33.31</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1342.10</t>
+          <t>451.25</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.11</v>
+        <v>0.38</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-100.31</t>
+          <t>-97.61</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>43310.31006160165</t>
+          <t>43751.04405737705</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>60192.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>3911.2</v>
+        <v>15301.2</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>4837.6</t>
+          <t>10672.7</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>5210.4</v>
+        <v>6284.02</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-926</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-24.67512899351711</t>
+          <t>593.3637320511897</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-211.9843094401649</t>
+          <t>3992.577467797077</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>3545.0</t>
+          <t>60192.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4834,7 +4834,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-19.15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>73.89</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>0.89</v>
+        <v>-0.41</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>33.60000000000001</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>33.29</v>
+        <v>33.32</v>
       </c>
       <c r="BA10" t="n">
-        <v>33.29</v>
+        <v>33.27</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>35.36</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>371.86</t>
+          <t>1342.10</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-101.33</t>
+          <t>-100.31</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>43310.31006160165</t>
+          <t>43751.04405737705</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>2754.0</t>
+          <t>3545.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>4555.4</v>
+        <v>3911.2</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>4830.4</t>
+          <t>4837.6</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>5228.98</v>
+        <v>5210.4</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-275</t>
+          <t>-926</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>9.381085633146125</t>
+          <t>-24.67512899351711</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-141.6088372990753</t>
+          <t>-211.9843094401649</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>2754.0</t>
+          <t>3545.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6879.323</t>
+          <t>4814.486</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>89.78</t>
+          <t>93.34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>37.73</t>
+          <t>26.40</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.37</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>8.06</v>
+        <v>2.25</v>
       </c>
       <c r="AV11" t="n">
-        <v>14.02</v>
+        <v>16.9</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17.49</t>
+          <t>18.19</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>15.34</v>
+        <v>15.56</v>
       </c>
       <c r="BA11" t="n">
-        <v>14.54</v>
+        <v>14.62</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.51</t>
+          <t>70.55</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.97</v>
+        <v>1.07</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.51</v>
+        <v>0.63</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-49.28</t>
+          <t>-38.41</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,48 +5605,48 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>24688715.34221311</t>
+          <t>24916407.8006135</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>126213557.0</t>
+          <t>90686885.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>114095044.6</v>
+        <v>131636381.6</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>60120293.6</t>
+          <t>68086166.1</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>15391974.5</v>
+        <v>17107665.4</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>53974750</t>
+          <t>63550215</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>9308845.08351049</t>
+          <t>11687047.71130428</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>28540492.77320272</t>
+          <t>24767162.16417013</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>126213557.0</t>
+          <t>90686885.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18233.797</t>
+          <t>6879.323</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>84.09</t>
+          <t>89.78</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>37.73</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,12 +6014,12 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6033,47 +6033,47 @@
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>11.11</v>
+        <v>8.06</v>
       </c>
       <c r="AV12" t="n">
-        <v>10.86</v>
+        <v>14.02</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>16.74</t>
+          <t>17.49</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>15.1</v>
+        <v>15.34</v>
       </c>
       <c r="BA12" t="n">
-        <v>14.46</v>
+        <v>14.54</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>100.50</t>
+          <t>88.51</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-60.50</t>
+          <t>-49.28</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,48 +6092,48 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>24688715.34221311</t>
+          <t>24916407.8006135</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>343629013.0</t>
+          <t>126213557.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>89597161.8</v>
+        <v>114095044.6</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>48670666.4</t>
+          <t>60120293.6</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>13149547.06</v>
+        <v>15391974.5</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>40926495</t>
+          <t>53974750</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>5812181.867202811</t>
+          <t>9308845.08351049</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>29105232.61563491</t>
+          <t>28540492.77320272</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>343629013.0</t>
+          <t>126213557.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,22 +6193,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2585.066</t>
+          <t>18233.797</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,74 +6320,74 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>18.6</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>84.09</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-03-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-03-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>18.25</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>3.44</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>48.96</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-03-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-03-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>18.25</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>18.25</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
           <t>20.6</t>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>14.18</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,12 +6501,12 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6516,51 +6516,51 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>95.65</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>13.64</v>
+        <v>11.11</v>
       </c>
       <c r="AV13" t="n">
-        <v>7.95</v>
+        <v>10.86</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>16.74</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>14.88</v>
+        <v>15.1</v>
       </c>
       <c r="BA13" t="n">
-        <v>14.39</v>
+        <v>14.46</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>14.78</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>103.21</t>
+          <t>100.50</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-70.42</t>
+          <t>-60.50</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,48 +6579,48 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>24688715.34221311</t>
+          <t>24916407.8006135</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>47177441.0</t>
+          <t>343629013.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>21955056.6</v>
+        <v>89597161.8</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>14738988.9</t>
+          <t>48670666.4</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>6368619.18</v>
+        <v>13149547.06</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>7216067</t>
+          <t>40926495</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>1577081.731124248</t>
+          <t>5812181.867202811</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>5578018.082836788</t>
+          <t>29105232.61563491</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>47177441.0</t>
+          <t>343629013.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3054.351</t>
+          <t>2585.066</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,22 +6817,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>48.96</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>14.18</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,12 +6988,12 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -7003,51 +7003,51 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>92.75</t>
+          <t>95.65</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>7.44</v>
+        <v>13.64</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.32</v>
+        <v>7.95</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>16.06</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>14.67</v>
+        <v>14.88</v>
       </c>
       <c r="BA14" t="n">
-        <v>14.32</v>
+        <v>14.39</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>14.76</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>74.82</t>
+          <t>103.21</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>0.39</v>
+        <v>0.61</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-78.06</t>
+          <t>-70.42</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,48 +7066,48 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>24688715.34221311</t>
+          <t>24916407.8006135</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>50475012.0</t>
+          <t>47177441.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>13351445.8</v>
+        <v>21955056.6</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>10252627.3</t>
+          <t>14738988.9</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>5539892.56</v>
+        <v>6368619.18</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>3098818</t>
+          <t>7216067</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>849638.7580856045</t>
+          <t>1577081.731124248</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>3531165.104452454</t>
+          <t>5578018.082836788</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>50475012.0</t>
+          <t>47177441.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -7177,12 +7177,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>197.75</t>
+          <t>3054.351</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>10.75</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-19.35</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>86.96</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>92.75</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-0.26</v>
+        <v>7.44</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.13</v>
+        <v>5.32</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>14.54</v>
+        <v>14.67</v>
       </c>
       <c r="BA15" t="n">
-        <v>14.29</v>
+        <v>14.32</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>14.76</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>74.82</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-82.16</t>
+          <t>-78.06</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>24688715.34221311</t>
+          <t>24916407.8006135</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>2980200.0</t>
+          <t>50475012.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>4535950.6</v>
+        <v>13351445.8</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>5623974.2</t>
+          <t>10252627.3</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>4700910.96</v>
+        <v>5539892.56</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-1088023</t>
+          <t>3098818</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>362088.5132916319</t>
+          <t>849638.7580856045</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>127665.2030301094</t>
+          <t>3531165.104452454</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>2980200.0</t>
+          <t>50475012.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,22 +7654,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>245.998</t>
+          <t>197.75</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>19.84</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>-19.35</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
+          <t>86.96</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
           <t>91.3</t>
         </is>
       </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>94.2</t>
-        </is>
-      </c>
       <c r="AU16" t="n">
-        <v>-0.13</v>
+        <v>-0.26</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.71</v>
+        <v>4.13</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>14.49</v>
+        <v>14.54</v>
       </c>
       <c r="BA16" t="n">
         <v>14.29</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>14.76</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>67.90</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="BD16" t="n">
         <v>0.27</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-84.35</t>
+          <t>-82.16</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>24688715.34221311</t>
+          <t>24916407.8006135</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>3724143.0</t>
+          <t>2980200.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>6145542.6</v>
+        <v>4535950.6</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>5704942.9</t>
+          <t>5623974.2</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>4687707.3</v>
+        <v>4700910.96</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>440599</t>
+          <t>-1088023</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>404710.9333391815</t>
+          <t>362088.5132916319</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>349692.8723185416</t>
+          <t>127665.2030301094</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>3724143.0</t>
+          <t>2980200.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>354.527</t>
+          <t>245.998</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>19.58</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>33.69</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,47 +8449,47 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>95.65</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>0.46</v>
+        <v>-0.13</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.87</v>
+        <v>4.71</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>15.17</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>14.43</v>
+        <v>14.49</v>
       </c>
       <c r="BA17" t="n">
         <v>14.29</v>
@@ -8501,14 +8501,14 @@
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>92.09</t>
+          <t>67.90</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-87.01</t>
+          <t>-84.35</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>24688715.34221311</t>
+          <t>24916407.8006135</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>5418487.0</t>
+          <t>3724143.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>7744171</v>
+        <v>6145542.6</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>5792449.0</t>
+          <t>5704942.9</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>4713125.22</v>
+        <v>4687707.3</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>1951722</t>
+          <t>440599</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>414714.217161116</t>
+          <t>404710.9333391815</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>574678.0472906418</t>
+          <t>349692.8723185416</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>5418487.0</t>
+          <t>3724143.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>275.729</t>
+          <t>354.527</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>19.58</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>38.30</t>
+          <t>33.69</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,33 +8915,33 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8951,32 +8951,32 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>92.75</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>1.6</v>
+        <v>0.46</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.14</v>
+        <v>4.87</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>14.36</v>
+        <v>14.43</v>
       </c>
       <c r="BA18" t="n">
         <v>14.29</v>
@@ -8988,14 +8988,14 @@
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>124.10</t>
+          <t>92.09</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-90.00</t>
+          <t>-87.01</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>24688715.34221311</t>
+          <t>24916407.8006135</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>4159387.0</t>
+          <t>5418487.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>7522921.2</v>
+        <v>7744171</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>5439467.1</t>
+          <t>5792449.0</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>4638633.98</v>
+        <v>4713125.22</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>2083454</t>
+          <t>1951722</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>385629.884410293</t>
+          <t>414714.217161116</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>694024.3669904033</t>
+          <t>574678.0472906418</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>4159387.0</t>
+          <t>5418487.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,17 +9180,17 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>15.4</t>
+        </is>
+      </c>
+      <c r="CS18" t="inlineStr">
+        <is>
           <t>15.1</t>
-        </is>
-      </c>
-      <c r="CR18" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
-      </c>
-      <c r="CS18" t="inlineStr">
-        <is>
-          <t>14.95</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>423.074</t>
+          <t>275.729</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>36.72</t>
+          <t>38.30</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>82.61</t>
+          <t>95.65</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>92.75</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.02</v>
+        <v>4.14</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>14.74</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>14.31</v>
+        <v>14.36</v>
       </c>
       <c r="BA19" t="n">
-        <v>14.28</v>
+        <v>14.29</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>14.77</t>
+          <t>14.76</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>173.07</t>
+          <t>124.10</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-93.10</t>
+          <t>-90.00</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>24688715.34221311</t>
+          <t>24916407.8006135</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>6397536.0</t>
+          <t>4159387.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>7153808.8</v>
+        <v>7522921.2</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>5232568.2</t>
+          <t>5439467.1</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>4644213</v>
+        <v>4638633.98</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>1921240</t>
+          <t>2083454</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>329558.1603048184</t>
+          <t>385629.884410293</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>974636.0963118337</t>
+          <t>694024.3669904033</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>6397536.0</t>
+          <t>4159387.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>58.04</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,14 +9667,14 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
           <t>15.2</t>
         </is>
       </c>
-      <c r="CR19" t="inlineStr">
-        <is>
-          <t>15.3</t>
-        </is>
-      </c>
       <c r="CS19" t="inlineStr">
         <is>
           <t>14.95</t>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2337.0</t>
+          <t>1445.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-12.90</t>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>-7.22</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9884,22 +9884,22 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2025-07-03 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>61.09</t>
+          <t>36.66</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-4.3</v>
+        <v>-6.46</v>
       </c>
       <c r="AV20" t="n">
-        <v>13.78</v>
+        <v>11.29</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>56.34</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>50.24</v>
+        <v>50.62</v>
       </c>
       <c r="BA20" t="n">
-        <v>46.66</v>
+        <v>46.81</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>47.87</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>28.01</t>
+          <t>11.28</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-75.36</t>
+          <t>-74.64</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,48 +9988,48 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>466626.8729508197</t>
+          <t>465909.9386503067</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>129758.0</t>
+          <t>77364.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>272892.4</v>
+        <v>233838.8</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>313314.6</t>
+          <t>305398.4</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>75287.02</v>
+        <v>76514.72</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-40422</t>
+          <t>-71559</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>44153.44074026583</t>
+          <t>39449.95631436231</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>31043.43031019717</t>
+          <t>13580.79197189293</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>129758.0</t>
+          <t>77364.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,22 +10089,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>390.71</t>
+          <t>376.43</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>49.83</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2585.0</t>
+          <t>2337.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>-12.90</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10371,22 +10371,22 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2025-07-03 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>62.45</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>79.78</t>
+          <t>61.09</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-2.29</v>
+        <v>-4.3</v>
       </c>
       <c r="AV21" t="n">
-        <v>15.98</v>
+        <v>13.78</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>57.72000000000001</t>
+          <t>57.16</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>49.77</v>
+        <v>50.24</v>
       </c>
       <c r="BA21" t="n">
-        <v>46.49</v>
+        <v>46.66</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>47.88</t>
+          <t>47.87</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>45.46</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.34</v>
+        <v>2.51</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-77.08</t>
+          <t>-75.36</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,48 +10475,48 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>466626.8729508197</t>
+          <t>465909.9386503067</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>146680.0</t>
+          <t>129758.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>393177.8</v>
+        <v>272892.4</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>302007.8</t>
+          <t>313314.6</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>73011.08</v>
+        <v>75287.02</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>91170</t>
+          <t>-40422</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>46537.07900027832</t>
+          <t>44153.44074026583</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>49267.71971098188</t>
+          <t>31043.43031019717</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>146680.0</t>
+          <t>129758.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>23.82</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,22 +10576,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>390.71</t>
+          <t>376.43</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>49.83</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5578.0</t>
+          <t>2585.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,17 +10713,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-7.02</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>61.99</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10858,22 +10858,22 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-07-03 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>39.79</t>
+          <t>18.44</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-9.79</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>62.45</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>79.78</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-1.31</v>
+        <v>-2.29</v>
       </c>
       <c r="AV22" t="n">
-        <v>17.76</v>
+        <v>15.98</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>57.96</t>
+          <t>57.72000000000001</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>49.22</v>
+        <v>49.77</v>
       </c>
       <c r="BA22" t="n">
-        <v>46.3</v>
+        <v>46.49</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>47.87</t>
+          <t>47.88</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>64.60</t>
+          <t>45.46</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.07</v>
+        <v>2.34</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-79.69</t>
+          <t>-77.08</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,48 +10962,48 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>466626.8729508197</t>
+          <t>465909.9386503067</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>334338.0</t>
+          <t>146680.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>466300.6</v>
+        <v>393177.8</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>287856.1</t>
+          <t>302007.8</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>70240.32000000001</v>
+        <v>73011.08</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>178444</t>
+          <t>91170</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>46040.59887105948</t>
+          <t>46537.07900027832</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>71729.78600813926</t>
+          <t>49267.71971098188</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>334338.0</t>
+          <t>146680.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,22 +11063,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>390.71</t>
+          <t>376.43</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>49.83</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8030.0</t>
+          <t>5578.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-10.97</t>
+          <t>-8.54</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>69.40</t>
+          <t>61.99</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11345,22 +11345,22 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-07-03 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>39.79</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>-9.79</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,266 +11371,266 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>97.86</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>6.49</v>
+        <v>-1.31</v>
       </c>
       <c r="AV23" t="n">
-        <v>17.22</v>
+        <v>17.76</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
+          <t>57.96</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>47.87</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>64.60</t>
+        </is>
+      </c>
+      <c r="BD23" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>-79.69</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2025/12/22</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>465909.9386503067</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>334338.0</t>
+        </is>
+      </c>
+      <c r="BK23" t="n">
+        <v>466300.6</v>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>287856.1</t>
+        </is>
+      </c>
+      <c r="BM23" t="n">
+        <v>70240.32000000001</v>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>178444</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>46040.59887105948</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>71729.78600813926</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>334338.0</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>45.55</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>2025/12/22</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
+          <t>25.58</t>
+        </is>
+      </c>
+      <c r="BV23" t="inlineStr">
+        <is>
+          <t>鑫科</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
+          <t>鑫科</t>
+        </is>
+      </c>
+      <c r="BX23" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BY23" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ23" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>-4.817042883161323</t>
+        </is>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>16.99821580807613</t>
+        </is>
+      </c>
+      <c r="CC23" t="inlineStr">
+        <is>
+          <t>27.20764306852215</t>
+        </is>
+      </c>
+      <c r="CD23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>價跌量縮</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="CH23" t="inlineStr">
+        <is>
+          <t>12.31</t>
+        </is>
+      </c>
+      <c r="CI23" t="inlineStr">
+        <is>
+          <t>376.43</t>
+        </is>
+      </c>
+      <c r="CJ23" t="inlineStr">
+        <is>
+          <t>2.61%</t>
+        </is>
+      </c>
+      <c r="CK23" t="inlineStr">
+        <is>
+          <t>-1.64%</t>
+        </is>
+      </c>
+      <c r="CL23" t="inlineStr">
+        <is>
+          <t>49.83</t>
+        </is>
+      </c>
+      <c r="CM23" t="inlineStr">
+        <is>
+          <t>5718</t>
+        </is>
+      </c>
+      <c r="CN23" t="inlineStr">
+        <is>
+          <t>貴金屬材料38.12%、鈦鎳34.48%、金紅石11.48%、薄膜濺鍍靶材10.85%、其他5.08% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO23" t="inlineStr">
+        <is>
+          <t>鑫科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CP23" t="inlineStr">
+        <is>
+          <t>其他電子業平上櫃</t>
+        </is>
+      </c>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="CS23" t="inlineStr">
+        <is>
           <t>57.0</t>
         </is>
       </c>
-      <c r="AZ23" t="n">
-        <v>48.63</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>46.11</v>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>47.85</t>
-        </is>
-      </c>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>89.53</t>
-        </is>
-      </c>
-      <c r="BD23" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>-82.97</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>2025/12/22</t>
-        </is>
-      </c>
-      <c r="BI23" t="inlineStr">
-        <is>
-          <t>466626.8729508197</t>
-        </is>
-      </c>
-      <c r="BJ23" t="inlineStr">
-        <is>
-          <t>481054.0</t>
-        </is>
-      </c>
-      <c r="BK23" t="n">
-        <v>432819.8</v>
-      </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>255508.3</t>
-        </is>
-      </c>
-      <c r="BM23" t="n">
-        <v>63726.7</v>
-      </c>
-      <c r="BN23" t="inlineStr">
-        <is>
-          <t>177311</t>
-        </is>
-      </c>
-      <c r="BO23" t="inlineStr">
-        <is>
-          <t>41369.83757340861</t>
-        </is>
-      </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>81150.45978950194</t>
-        </is>
-      </c>
-      <c r="BQ23" t="inlineStr">
-        <is>
-          <t>481054.0</t>
-        </is>
-      </c>
-      <c r="BR23" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="BS23" t="inlineStr">
-        <is>
-          <t>45.55</t>
-        </is>
-      </c>
-      <c r="BT23" t="inlineStr">
-        <is>
-          <t>2025/12/22</t>
-        </is>
-      </c>
-      <c r="BU23" t="inlineStr">
-        <is>
-          <t>33.26</t>
-        </is>
-      </c>
-      <c r="BV23" t="inlineStr">
-        <is>
-          <t>鑫科</t>
-        </is>
-      </c>
-      <c r="BW23" t="inlineStr">
-        <is>
-          <t>鑫科</t>
-        </is>
-      </c>
-      <c r="BX23" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BY23" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ23" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="CA23" t="inlineStr">
-        <is>
-          <t>-4.817042883161323</t>
-        </is>
-      </c>
-      <c r="CB23" t="inlineStr">
-        <is>
-          <t>16.99821580807613</t>
-        </is>
-      </c>
-      <c r="CC23" t="inlineStr">
-        <is>
-          <t>27.20764306852215</t>
-        </is>
-      </c>
-      <c r="CD23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
-        </is>
-      </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>3.68</t>
-        </is>
-      </c>
-      <c r="CG23" t="inlineStr">
-        <is>
-          <t>0.73</t>
-        </is>
-      </c>
-      <c r="CH23" t="inlineStr">
-        <is>
-          <t>12.31</t>
-        </is>
-      </c>
-      <c r="CI23" t="inlineStr">
-        <is>
-          <t>390.71</t>
-        </is>
-      </c>
-      <c r="CJ23" t="inlineStr">
-        <is>
-          <t>2.61%</t>
-        </is>
-      </c>
-      <c r="CK23" t="inlineStr">
-        <is>
-          <t>-1.64%</t>
-        </is>
-      </c>
-      <c r="CL23" t="inlineStr">
-        <is>
-          <t>50.79</t>
-        </is>
-      </c>
-      <c r="CM23" t="inlineStr">
-        <is>
-          <t>5935</t>
-        </is>
-      </c>
-      <c r="CN23" t="inlineStr">
-        <is>
-          <t>貴金屬材料38.12%、鈦鎳34.48%、金紅石11.48%、薄膜濺鍍靶材10.85%、其他5.08% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO23" t="inlineStr">
-        <is>
-          <t>鑫科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CP23" t="inlineStr">
-        <is>
-          <t>其他電子業平上櫃</t>
-        </is>
-      </c>
-      <c r="CQ23" t="inlineStr">
-        <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="CR23" t="inlineStr">
-        <is>
-          <t>61.9</t>
-        </is>
-      </c>
-      <c r="CS23" t="inlineStr">
-        <is>
-          <t>57.6</t>
-        </is>
-      </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4747.0</t>
+          <t>8030.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,74 +11677,74 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>60.7</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-15.18</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-0.71</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>69.40</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2025-12-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2025-07-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
           <t>56.8</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>-3.84</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>80.30</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2025-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>2025-07-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2025-07-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>56.8</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
-      </c>
       <c r="T24" t="inlineStr">
         <is>
           <t>67.0</t>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11832,22 +11832,22 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2025-07-03 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>33.87</t>
+          <t>57.29</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,17 +11858,17 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>94.31</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
@@ -11877,47 +11877,47 @@
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>3.54</v>
+        <v>6.49</v>
       </c>
       <c r="AV24" t="n">
-        <v>14.63</v>
+        <v>17.22</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>54.86</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>47.86</v>
+        <v>48.63</v>
       </c>
       <c r="BA24" t="n">
-        <v>45.85</v>
+        <v>46.11</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>47.77</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>103.04</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>2.74</v>
+        <v>3.29</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-86.78</t>
+          <t>-82.97</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,48 +11936,48 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>466626.8729508197</t>
+          <t>465909.9386503067</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>272632.0</t>
+          <t>481054.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>376958</v>
+        <v>432819.8</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>209075.2</t>
+          <t>255508.3</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>54433.72</v>
+        <v>63726.7</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>167882</t>
+          <t>177311</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>34136.99717048254</t>
+          <t>41369.83757340861</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>75990.76305610931</t>
+          <t>81150.45978950194</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>272632.0</t>
+          <t>481054.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>24.70</t>
+          <t>33.26</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,22 +12037,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>390.71</t>
+          <t>376.43</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>49.83</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12640.0</t>
+          <t>4747.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,22 +12174,22 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>89.27</t>
+          <t>80.30</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12319,22 +12319,22 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2025-07-03 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>33.87</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,66 +12345,66 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>99.29</t>
+          <t>94.31</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>99.76</t>
+          <t>97.86</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>7.78</v>
+        <v>3.54</v>
       </c>
       <c r="AV25" t="n">
-        <v>12.86</v>
+        <v>14.63</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>53.35</t>
+          <t>54.86</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>47.27</v>
+        <v>47.86</v>
       </c>
       <c r="BA25" t="n">
-        <v>45.66</v>
+        <v>45.85</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>47.73</t>
+          <t>47.77</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>138.46</t>
+          <t>103.04</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>2.39</v>
+        <v>2.74</v>
       </c>
       <c r="BE25" t="n">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-90.18</t>
+          <t>-86.78</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,48 +12423,48 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>466626.8729508197</t>
+          <t>465909.9386503067</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>731185.0</t>
+          <t>272632.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>353736.8</v>
+        <v>376958</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>186898.1</t>
+          <t>209075.2</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>49202.24</v>
+        <v>54433.72</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>166838</t>
+          <t>167882</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>26527.22155491404</t>
+          <t>34136.99717048254</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>88236.7404706873</t>
+          <t>75990.76305610931</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>731185.0</t>
+          <t>272632.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>24.70</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12529,17 +12529,17 @@
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>390.71</t>
+          <t>376.43</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>49.83</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>9087.0</t>
+          <t>12640.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-5.3</t>
+          <t>-9.11</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.02</t>
+          <t>89.27</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12806,92 +12806,92 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2025-07-03 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>64.83</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.29</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.76</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>13.03</v>
+        <v>7.78</v>
       </c>
       <c r="AV26" t="n">
-        <v>9.050000000000001</v>
+        <v>12.86</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>50.95999999999999</t>
+          <t>53.35</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>46.73</v>
+        <v>47.27</v>
       </c>
       <c r="BA26" t="n">
-        <v>45.46</v>
+        <v>45.66</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>47.69</t>
+          <t>47.73</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>180.11</t>
+          <t>138.46</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>1.83</v>
+        <v>2.39</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-93.58</t>
+          <t>-90.18</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>466626.8729508197</t>
+          <t>465909.9386503067</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>512294.0</t>
+          <t>731185.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>210837.8</v>
+        <v>353736.8</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>119783.6</t>
+          <t>186898.1</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>34941.72</v>
+        <v>49202.24</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>91054</t>
+          <t>166838</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>15307.30902477344</t>
+          <t>26527.22155491404</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>53449.00318898856</t>
+          <t>88236.7404706873</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>512294.0</t>
+          <t>731185.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>390.71</t>
+          <t>376.43</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>49.83</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3251.0</t>
+          <t>9087.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>58.32</t>
+          <t>76.02</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13293,22 +13293,22 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2025-07-03 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>64.83</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13338,47 +13338,47 @@
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>8.74</v>
+        <v>13.03</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.38</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>48.19</t>
+          <t>50.95999999999999</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>46.17</v>
+        <v>46.73</v>
       </c>
       <c r="BA27" t="n">
-        <v>45.26</v>
+        <v>45.46</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>47.69</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>202.90</t>
+          <t>180.11</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>1.09</v>
+        <v>1.83</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.36</v>
+        <v>0.65</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-96.47</t>
+          <t>-93.58</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>466626.8729508197</t>
+          <t>465909.9386503067</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>166934.0</t>
+          <t>512294.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>109411.6</v>
+        <v>210837.8</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>69108.9</t>
+          <t>119783.6</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>25047.98</v>
+        <v>34941.72</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>40302</t>
+          <t>91054</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>8372.455540370695</t>
+          <t>15307.30902477344</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>25295.94981552642</t>
+          <t>53449.00318898856</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>166934.0</t>
+          <t>512294.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>15.04</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>390.71</t>
+          <t>376.43</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>49.83</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3945.0</t>
+          <t>3251.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>58.32</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13780,22 +13780,22 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2025-07-03 00:00:00</t>
+          <t>2026-01-05 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13821,51 +13821,51 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>80.41</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>7.71</v>
+        <v>8.74</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.48</v>
+        <v>4.38</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-5.40</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>46.42</t>
+          <t>48.19</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>45.74</v>
+        <v>46.17</v>
       </c>
       <c r="BA28" t="n">
-        <v>45.14</v>
+        <v>45.26</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>269.24</t>
+          <t>202.90</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>0.65</v>
+        <v>1.09</v>
       </c>
       <c r="BE28" t="n">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-98.26</t>
+          <t>-96.47</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>466626.8729508197</t>
+          <t>465909.9386503067</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>201745.0</t>
+          <t>166934.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>78196.8</v>
+        <v>109411.6</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>53380.4</t>
+          <t>69108.9</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>21972.36</v>
+        <v>25047.98</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>24816</t>
+          <t>40302</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>5295.456581251472</t>
+          <t>8372.455540370695</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>21176.73250288313</t>
+          <t>25295.94981552642</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>201745.0</t>
+          <t>166934.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>390.71</t>
+          <t>376.43</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>49.83</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
